--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 06/02. Trả bảo hành/TBH_AnhTuanNB+NamAnh_200626.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 06/02. Trả bảo hành/TBH_AnhTuanNB+NamAnh_200626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 06\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12634162-8A79-4FEB-87B7-946B24EC728B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F557EAFB-C024-457C-9C24-B132E0C04C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
   <si>
     <t>Công Ty Cổ Phần Công Nghệ Điện Tử &amp; Viễn Thông Việt Nam</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>ĐL Nam Anh</t>
+  </si>
+  <si>
+    <t>eSIM: 01388618982</t>
   </si>
 </sst>
 </file>
@@ -629,6 +632,15 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -672,15 +684,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1064,77 +1067,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A1" s="53"/>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="58" t="s">
+      <c r="A1" s="56"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="62" t="s">
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="49"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="47" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="34"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
@@ -1144,12 +1147,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
       <c r="E7" s="34"/>
       <c r="F7" s="36"/>
       <c r="G7" s="36"/>
@@ -1157,12 +1160,12 @@
       <c r="I7" s="36"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
       <c r="E8" s="34"/>
       <c r="F8" s="35"/>
       <c r="G8" s="35"/>
@@ -1170,12 +1173,12 @@
       <c r="I8" s="35"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
       <c r="E9" s="34"/>
       <c r="F9" s="35"/>
       <c r="G9" s="35"/>
@@ -1322,7 +1325,9 @@
       <c r="E15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="42"/>
+      <c r="F15" s="42" t="s">
+        <v>62</v>
+      </c>
       <c r="G15" s="43" t="s">
         <v>47</v>
       </c>
@@ -1532,34 +1537,34 @@
       <c r="I24" s="12"/>
     </row>
     <row r="25" spans="1:10 16384:16384" ht="15.95" customHeight="1">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
       <c r="E25" s="15"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="55" t="s">
+      <c r="G25" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
     </row>
     <row r="26" spans="1:10 16384:16384" ht="15.95" customHeight="1">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="32"/>
       <c r="F26" s="33"/>
-      <c r="G26" s="56" t="s">
+      <c r="G26" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
     </row>
     <row r="27" spans="1:10 16384:16384" ht="15.95" customHeight="1">
       <c r="A27" s="18"/>
@@ -1617,19 +1622,19 @@
       <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:10 16384:16384" ht="15.95" customHeight="1">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
       <c r="E32" s="15"/>
       <c r="F32" s="29"/>
-      <c r="G32" s="54" t="s">
+      <c r="G32" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
     </row>
     <row r="33" spans="1:9" ht="15.95" customHeight="1">
       <c r="A33" s="29"/>
@@ -1643,12 +1648,13 @@
       <c r="I33" s="31"/>
     </row>
     <row r="35" spans="1:9" ht="17.25">
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
     </row>
     <row r="74" ht="20.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
@@ -1665,7 +1671,6 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.9" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
